--- a/Excel/Aula 05/LAN HOUSE.xlsx
+++ b/Excel/Aula 05/LAN HOUSE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tosenac-my.sharepoint.com/personal/jaderson_gpi_to_senac_br/Documents/Excel Avançado/Aula 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\Jaderson-Araujo\Excel\Aula 05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3A77850E-0D30-4214-AF91-2D962510F016}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{3F5DE40D-6212-4FA9-B2D6-906CBED8D749}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFBD6BD-7A31-435B-8F92-EB21A65ECFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,17 @@
     <sheet name="Plan3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -160,7 +171,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -169,24 +180,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -198,7 +205,7 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -313,9 +320,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -353,9 +360,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -388,26 +395,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -440,26 +430,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -634,77 +607,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" style="1" customWidth="1"/>
-    <col min="7" max="8" width="14.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="1" customWidth="1"/>
+    <col min="7" max="8" width="14.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>10</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="E2" s="11"/>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -714,14 +681,14 @@
       <c r="C5" s="4">
         <v>0.4201388888888889</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="17"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="15"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -731,14 +698,14 @@
       <c r="C6" s="4">
         <v>0.44930555555555557</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="17"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="15"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
@@ -748,14 +715,14 @@
       <c r="C7" s="4">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="15"/>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
@@ -765,14 +732,14 @@
       <c r="C8" s="4">
         <v>0.50347222222222221</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="15"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -782,14 +749,14 @@
       <c r="C9" s="4">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="17"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="15"/>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
@@ -799,14 +766,14 @@
       <c r="C10" s="4">
         <v>0.6875</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="15"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -816,24 +783,24 @@
       <c r="C11" s="4">
         <v>0.75</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="17"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="15"/>
       <c r="I11" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H16" s="18"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H17" s="18"/>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H14" s="16"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H15" s="16"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H16" s="16"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H17" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -848,7 +815,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -857,7 +824,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
